--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:55:04-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.10</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-04-23T10:10:52-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-06-10T07:35:08-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-11T12:11:14-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T12:11:14-05:00</t>
+    <t>2026-06-12T09:38:46-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:38:46-05:00</t>
+    <t>2026-06-21T22:38:39-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T22:38:39-05:00</t>
+    <t>2026-06-21T23:16:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -61,19 +61,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T23:16:04-05:00</t>
+    <t>2026-06-22T08:51:47-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -61,19 +61,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:51:47-05:00</t>
+    <t>2026-06-22T09:21:59-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:21:59-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T19:24:07-05:00</t>
+    <t>2026-08-19T10:07:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/ValueSet-presence-valueset.xlsx
+++ b/build/temp/pages/ValueSet-presence-valueset.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,19 +61,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:01:54-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
